--- a/mario/test/tables/test_IOT_standard.xlsx
+++ b/mario/test/tables/test_IOT_standard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzorinaldi/Documents/GitHub/MARIO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzorinaldi/Documents/GitHub/MARIO/mario/test/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87457F36-C9C5-7E40-A2C7-43E7881E354B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4185F95E-A3E6-C74C-9BB0-93132FB996D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25600" yWindow="600" windowWidth="25600" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="flows" sheetId="1" r:id="rId1"/>
